--- a/servers/maze_main_server/conf.d/data/maze_patrol_v8【迷宫-巡逻守卫】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_patrol_v8【迷宫-巡逻守卫】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37B8F905-22D9-4A99-ADE3-A7CB3981F9D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80CB1FC-35D8-4532-8017-B2D6C2956D14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_patrol_v8" sheetId="1" r:id="rId1"/>
@@ -778,7 +778,7 @@
         <v>60401</v>
       </c>
       <c r="E20" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.15">
@@ -795,7 +795,7 @@
         <v>60402</v>
       </c>
       <c r="E21" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.15">
@@ -812,7 +812,7 @@
         <v>60403</v>
       </c>
       <c r="E22" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.15">
@@ -829,7 +829,7 @@
         <v>70401</v>
       </c>
       <c r="E23" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.15">
@@ -846,7 +846,7 @@
         <v>70402</v>
       </c>
       <c r="E24" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.15">
@@ -863,7 +863,7 @@
         <v>70403</v>
       </c>
       <c r="E25" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.15">
@@ -880,7 +880,7 @@
         <v>80401</v>
       </c>
       <c r="E26" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.15">
@@ -897,7 +897,7 @@
         <v>80402</v>
       </c>
       <c r="E27" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.15">
@@ -914,7 +914,7 @@
         <v>80403</v>
       </c>
       <c r="E28" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.15">
@@ -931,7 +931,7 @@
         <v>90401</v>
       </c>
       <c r="E29" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.15">
@@ -948,7 +948,7 @@
         <v>90402</v>
       </c>
       <c r="E30" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.15">
@@ -965,7 +965,7 @@
         <v>90403</v>
       </c>
       <c r="E31" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.15">
@@ -982,7 +982,7 @@
         <v>100401</v>
       </c>
       <c r="E32" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.15">
@@ -999,7 +999,7 @@
         <v>100402</v>
       </c>
       <c r="E33" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.15">
@@ -1016,7 +1016,7 @@
         <v>100403</v>
       </c>
       <c r="E34" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.15">
@@ -1033,7 +1033,7 @@
         <v>110401</v>
       </c>
       <c r="E35" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.15">
@@ -1050,7 +1050,7 @@
         <v>110402</v>
       </c>
       <c r="E36" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.15">
@@ -1067,7 +1067,7 @@
         <v>110403</v>
       </c>
       <c r="E37" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.15">
@@ -1084,7 +1084,7 @@
         <v>120401</v>
       </c>
       <c r="E38" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.15">
@@ -1101,7 +1101,7 @@
         <v>120402</v>
       </c>
       <c r="E39" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.15">
@@ -1118,7 +1118,7 @@
         <v>120403</v>
       </c>
       <c r="E40" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.15">
@@ -1135,7 +1135,7 @@
         <v>130401</v>
       </c>
       <c r="E41" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.15">
@@ -1152,7 +1152,7 @@
         <v>130402</v>
       </c>
       <c r="E42" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.15">
@@ -1169,7 +1169,7 @@
         <v>130403</v>
       </c>
       <c r="E43" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.15">
@@ -1186,7 +1186,7 @@
         <v>140401</v>
       </c>
       <c r="E44" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.15">
@@ -1203,7 +1203,7 @@
         <v>140402</v>
       </c>
       <c r="E45" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.15">
@@ -1220,7 +1220,7 @@
         <v>140403</v>
       </c>
       <c r="E46" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.15">
@@ -1237,7 +1237,7 @@
         <v>150401</v>
       </c>
       <c r="E47" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.15">
@@ -1254,7 +1254,7 @@
         <v>150402</v>
       </c>
       <c r="E48" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.15">
@@ -1271,7 +1271,7 @@
         <v>150403</v>
       </c>
       <c r="E49" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.15">
@@ -1288,7 +1288,7 @@
         <v>160401</v>
       </c>
       <c r="E50" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.15">
@@ -1305,7 +1305,7 @@
         <v>160402</v>
       </c>
       <c r="E51" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.15">
@@ -1322,7 +1322,7 @@
         <v>160403</v>
       </c>
       <c r="E52" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.15">
@@ -1339,7 +1339,7 @@
         <v>170401</v>
       </c>
       <c r="E53" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.15">
@@ -1356,7 +1356,7 @@
         <v>170402</v>
       </c>
       <c r="E54" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.15">
@@ -1373,7 +1373,7 @@
         <v>170403</v>
       </c>
       <c r="E55" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.15">
@@ -1390,7 +1390,7 @@
         <v>180401</v>
       </c>
       <c r="E56" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.15">
@@ -1407,7 +1407,7 @@
         <v>180402</v>
       </c>
       <c r="E57" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.15">
@@ -1424,7 +1424,7 @@
         <v>180403</v>
       </c>
       <c r="E58" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.15">
@@ -1441,7 +1441,7 @@
         <v>190401</v>
       </c>
       <c r="E59" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.15">
@@ -1458,7 +1458,7 @@
         <v>190402</v>
       </c>
       <c r="E60" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.15">
@@ -1475,7 +1475,7 @@
         <v>190403</v>
       </c>
       <c r="E61" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.15">
@@ -1492,7 +1492,7 @@
         <v>200401</v>
       </c>
       <c r="E62" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.15">
@@ -1509,7 +1509,7 @@
         <v>200402</v>
       </c>
       <c r="E63" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.15">
@@ -1526,7 +1526,7 @@
         <v>200403</v>
       </c>
       <c r="E64" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.15">
@@ -1543,7 +1543,7 @@
         <v>210401</v>
       </c>
       <c r="E65" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.15">
@@ -1560,7 +1560,7 @@
         <v>210402</v>
       </c>
       <c r="E66" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.15">
@@ -1577,7 +1577,7 @@
         <v>210403</v>
       </c>
       <c r="E67" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.15">
@@ -1594,7 +1594,7 @@
         <v>220401</v>
       </c>
       <c r="E68" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.15">
@@ -1611,7 +1611,7 @@
         <v>220402</v>
       </c>
       <c r="E69" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.15">
@@ -1628,7 +1628,7 @@
         <v>220403</v>
       </c>
       <c r="E70" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.15">
@@ -1645,7 +1645,7 @@
         <v>230401</v>
       </c>
       <c r="E71" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.15">
@@ -1662,7 +1662,7 @@
         <v>230402</v>
       </c>
       <c r="E72" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.15">
@@ -1679,7 +1679,7 @@
         <v>230403</v>
       </c>
       <c r="E73" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.15">
@@ -1696,7 +1696,7 @@
         <v>240401</v>
       </c>
       <c r="E74" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.15">
@@ -1713,7 +1713,7 @@
         <v>240402</v>
       </c>
       <c r="E75" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.15">
@@ -1730,7 +1730,7 @@
         <v>240403</v>
       </c>
       <c r="E76" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.15">
@@ -1747,7 +1747,7 @@
         <v>250401</v>
       </c>
       <c r="E77" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.15">
@@ -1764,7 +1764,7 @@
         <v>250402</v>
       </c>
       <c r="E78" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.15">
@@ -1781,7 +1781,7 @@
         <v>250403</v>
       </c>
       <c r="E79" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.15">
@@ -1798,7 +1798,7 @@
         <v>260401</v>
       </c>
       <c r="E80" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.15">
@@ -1815,7 +1815,7 @@
         <v>260402</v>
       </c>
       <c r="E81" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.15">
@@ -1832,7 +1832,7 @@
         <v>260403</v>
       </c>
       <c r="E82" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.15">
@@ -1849,7 +1849,7 @@
         <v>270401</v>
       </c>
       <c r="E83" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.15">
@@ -1866,7 +1866,7 @@
         <v>270402</v>
       </c>
       <c r="E84" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.15">
@@ -1883,7 +1883,7 @@
         <v>270403</v>
       </c>
       <c r="E85" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.15">
@@ -1900,7 +1900,7 @@
         <v>280401</v>
       </c>
       <c r="E86" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.15">
@@ -1917,7 +1917,7 @@
         <v>280402</v>
       </c>
       <c r="E87" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.15">
@@ -1934,7 +1934,7 @@
         <v>280403</v>
       </c>
       <c r="E88" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.15">
@@ -1951,7 +1951,7 @@
         <v>290401</v>
       </c>
       <c r="E89" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.15">
@@ -1968,7 +1968,7 @@
         <v>290402</v>
       </c>
       <c r="E90" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.15">
@@ -1985,7 +1985,7 @@
         <v>290403</v>
       </c>
       <c r="E91" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.15">
@@ -2002,7 +2002,7 @@
         <v>300401</v>
       </c>
       <c r="E92" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.15">
@@ -2019,7 +2019,7 @@
         <v>300402</v>
       </c>
       <c r="E93" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.15">
@@ -2036,7 +2036,7 @@
         <v>300403</v>
       </c>
       <c r="E94" s="1">
-        <v>180</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
